--- a/artfynd/A 33759-2025 artfynd.xlsx
+++ b/artfynd/A 33759-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113678714</v>
       </c>
       <c r="B2" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,6 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Bärmyran, Ång</t>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,12 +774,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -789,12 +788,7 @@
         <v>113678718</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,6 +814,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Bärmyran, Ång</t>
@@ -870,6 +867,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -886,12 +884,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -900,12 +898,7 @@
         <v>113678716</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,6 +924,9 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Orrkullen, Ång</t>
@@ -981,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,12 +994,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1011,12 +1008,7 @@
         <v>113678715</v>
       </c>
       <c r="B5" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,6 +1034,9 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Orrkullen, Ång</t>
@@ -1092,6 +1087,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,12 +1104,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 33759-2025 artfynd.xlsx
+++ b/artfynd/A 33759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113678714</v>
       </c>
       <c r="B2" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113678718</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>113678716</v>
       </c>
       <c r="B4" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>113678715</v>
       </c>
       <c r="B5" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33759-2025 artfynd.xlsx
+++ b/artfynd/A 33759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113678714</v>
       </c>
       <c r="B2" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113678718</v>
       </c>
       <c r="B3" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>113678716</v>
       </c>
       <c r="B4" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>113678715</v>
       </c>
       <c r="B5" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33759-2025 artfynd.xlsx
+++ b/artfynd/A 33759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113678714</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113678718</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>113678716</v>
       </c>
       <c r="B4" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>113678715</v>
       </c>
       <c r="B5" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
